--- a/excel_project/部门考勤数据/采购部 (Procurement)_异常考勤数据.xlsx
+++ b/excel_project/部门考勤数据/采购部 (Procurement)_异常考勤数据.xlsx
@@ -478,12 +478,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25-09-28 星期日</t>
+          <t>25-10-30 星期四</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25-09-28 星期日</t>
+          <t>25-11-17 星期一</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,14 +528,10 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>18:07</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
+          <t>缺卡</t>
         </is>
       </c>
     </row>
@@ -552,34 +548,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25-09-29 星期一</t>
+          <t>25-11-18 星期二</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缺卡</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>金韵斐-Catherine Jin</t>
+          <t>钱惠珺-Stefan Qian</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -589,19 +581,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25-10-09 星期四</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>25-10-29 星期三</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>缺卡</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>迟到</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>缺卡</t>
+          <t>早退</t>
         </is>
       </c>
     </row>
